--- a/java/jdk8/javase_api_doc.xlsx
+++ b/java/jdk8/javase_api_doc.xlsx
@@ -4,26 +4,33 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564" activeTab="1"/>
+    <workbookView windowWidth="22368" windowHeight="9564"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="120">
-  <si>
-    <t>java.util.concurrent</t>
-  </si>
-  <si>
-    <t>java.util.concurrent.atomic</t>
-  </si>
-  <si>
-    <t>java.util.concurrent.locks</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="282">
+  <si>
+    <t>java.nio.channels</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Classes</t>
+    </r>
   </si>
   <si>
     <r>
@@ -38,6 +45,132 @@
     </r>
   </si>
   <si>
+    <t>AbstractInterruptibleChannel</t>
+  </si>
+  <si>
+    <t>AbstractSelectableChannel</t>
+  </si>
+  <si>
+    <t>Buffer</t>
+  </si>
+  <si>
+    <t>AsynchronousByteChannel</t>
+  </si>
+  <si>
+    <t>AbstractSelectionKey</t>
+  </si>
+  <si>
+    <t>Charset</t>
+  </si>
+  <si>
+    <t>CopyOption</t>
+  </si>
+  <si>
+    <t>AclFileAttributeView</t>
+  </si>
+  <si>
+    <t>ByteBuffer</t>
+  </si>
+  <si>
+    <t>AsynchronousChannel</t>
+  </si>
+  <si>
+    <t>AbstractSelector</t>
+  </si>
+  <si>
+    <t>CharsetDecoder</t>
+  </si>
+  <si>
+    <t>DirectoryStream</t>
+  </si>
+  <si>
+    <t>AttributeView</t>
+  </si>
+  <si>
+    <t>ByteOrder</t>
+  </si>
+  <si>
+    <t>ByteChannel</t>
+  </si>
+  <si>
+    <t>AsynchronousChannelProvider</t>
+  </si>
+  <si>
+    <t>CharsetEncoder</t>
+  </si>
+  <si>
+    <t>DirectoryStream.Filter</t>
+  </si>
+  <si>
+    <t>BasicFileAttributes</t>
+  </si>
+  <si>
+    <t>CharBuffer</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>SelectorProvider</t>
+  </si>
+  <si>
+    <t>CoderResult</t>
+  </si>
+  <si>
+    <t>FileVisitor</t>
+  </si>
+  <si>
+    <t>BasicFileAttributeView</t>
+  </si>
+  <si>
+    <t>DoubleBuffer</t>
+  </si>
+  <si>
+    <t>CompletionHandler</t>
+  </si>
+  <si>
+    <t>CodingErrorAction</t>
+  </si>
+  <si>
+    <t>OpenOption</t>
+  </si>
+  <si>
+    <t>DosFileAttributes</t>
+  </si>
+  <si>
+    <t>FloatBuffer</t>
+  </si>
+  <si>
+    <t>GatheringByteChannel</t>
+  </si>
+  <si>
+    <t>StandardCharsets</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>DosFileAttributeView</t>
+  </si>
+  <si>
+    <t>IntBuffer</t>
+  </si>
+  <si>
+    <t>InterruptibleChannel</t>
+  </si>
+  <si>
+    <t>PathMatcher</t>
+  </si>
+  <si>
+    <t>FileAttribute</t>
+  </si>
+  <si>
+    <t>LongBuffer</t>
+  </si>
+  <si>
+    <t>MulticastChannel</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -46,269 +179,182 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>Classes</t>
+      <t>Exceptions</t>
     </r>
   </si>
   <si>
-    <t>BlockingDeque</t>
-  </si>
-  <si>
-    <t>AtomicBoolean</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>BlockingQueue</t>
-  </si>
-  <si>
-    <t>AtomicInteger</t>
-  </si>
-  <si>
-    <t>Lock</t>
-  </si>
-  <si>
-    <t>Callable</t>
-  </si>
-  <si>
-    <t>AtomicIntegerArray</t>
-  </si>
-  <si>
-    <t>ReadWriteLock</t>
-  </si>
-  <si>
-    <t>CompletableFuture.AsynchronousCompletionTask</t>
-  </si>
-  <si>
-    <t>AtomicIntegerFieldUpdater</t>
-  </si>
-  <si>
-    <t>CompletionService</t>
-  </si>
-  <si>
-    <t>AtomicLong</t>
-  </si>
-  <si>
-    <t>CompletionStage</t>
-  </si>
-  <si>
-    <t>AtomicLongArray</t>
-  </si>
-  <si>
-    <t>ConcurrentMap</t>
-  </si>
-  <si>
-    <t>AtomicLongFieldUpdater</t>
-  </si>
-  <si>
-    <t>AbstractOwnableSynchronizer</t>
-  </si>
-  <si>
-    <t>ConcurrentNavigableMap</t>
-  </si>
-  <si>
-    <t>AtomicMarkableReference</t>
-  </si>
-  <si>
-    <t>AbstractQueuedLongSynchronizer</t>
-  </si>
-  <si>
-    <t>Delayed</t>
-  </si>
-  <si>
-    <t>AtomicReference</t>
-  </si>
-  <si>
-    <t>AbstractQueuedSynchronizer</t>
-  </si>
-  <si>
-    <t>Executor</t>
-  </si>
-  <si>
-    <t>AtomicReferenceArray</t>
-  </si>
-  <si>
-    <t>LockSupport</t>
-  </si>
-  <si>
-    <t>ExecutorService</t>
-  </si>
-  <si>
-    <t>AtomicReferenceFieldUpdater</t>
-  </si>
-  <si>
-    <t>ReentrantLock</t>
-  </si>
-  <si>
-    <t>ForkJoinPool.ForkJoinWorkerThreadFactory</t>
-  </si>
-  <si>
-    <t>AtomicStampedReference</t>
-  </si>
-  <si>
-    <t>ReentrantReadWriteLock</t>
-  </si>
-  <si>
-    <t>ForkJoinPool.ManagedBlocker</t>
-  </si>
-  <si>
-    <t>DoubleAccumulator</t>
-  </si>
-  <si>
-    <t>ReentrantReadWriteLock.ReadLock</t>
-  </si>
-  <si>
-    <t>Future</t>
-  </si>
-  <si>
-    <t>DoubleAdder</t>
-  </si>
-  <si>
-    <t>ReentrantReadWriteLock.WriteLock</t>
-  </si>
-  <si>
-    <t>RejectedExecutionHandler</t>
-  </si>
-  <si>
-    <t>LongAccumulator</t>
-  </si>
-  <si>
-    <t>StampedLock</t>
-  </si>
-  <si>
-    <t>RunnableFuture</t>
-  </si>
-  <si>
-    <t>LongAdder</t>
-  </si>
-  <si>
-    <t>RunnableScheduledFuture</t>
-  </si>
-  <si>
-    <t>ScheduledExecutorService</t>
-  </si>
-  <si>
-    <t>ScheduledFuture</t>
-  </si>
-  <si>
-    <t>ThreadFactory</t>
-  </si>
-  <si>
-    <t>TransferQueue</t>
-  </si>
-  <si>
-    <t>AbstractExecutorService</t>
-  </si>
-  <si>
-    <t>ArrayBlockingQueue</t>
-  </si>
-  <si>
-    <t>CompletableFuture</t>
-  </si>
-  <si>
-    <t>ConcurrentHashMap</t>
-  </si>
-  <si>
-    <t>ConcurrentHashMap.KeySetView</t>
-  </si>
-  <si>
-    <t>ConcurrentLinkedDeque</t>
-  </si>
-  <si>
-    <t>ConcurrentLinkedQueue</t>
-  </si>
-  <si>
-    <t>ConcurrentSkipListMap</t>
-  </si>
-  <si>
-    <t>ConcurrentSkipListSet</t>
-  </si>
-  <si>
-    <t>CopyOnWriteArrayList</t>
-  </si>
-  <si>
-    <t>CopyOnWriteArraySet</t>
-  </si>
-  <si>
-    <t>CountDownLatch</t>
-  </si>
-  <si>
-    <t>CountedCompleter</t>
-  </si>
-  <si>
-    <t>CyclicBarrier</t>
-  </si>
-  <si>
-    <t>DelayQueue</t>
-  </si>
-  <si>
-    <t>Exchanger</t>
-  </si>
-  <si>
-    <t>ExecutorCompletionService</t>
-  </si>
-  <si>
-    <t>Executors</t>
-  </si>
-  <si>
-    <t>ForkJoinPool</t>
-  </si>
-  <si>
-    <t>ForkJoinTask</t>
-  </si>
-  <si>
-    <t>ForkJoinWorkerThread</t>
-  </si>
-  <si>
-    <t>FutureTask</t>
-  </si>
-  <si>
-    <t>LinkedBlockingDeque</t>
-  </si>
-  <si>
-    <t>LinkedBlockingQueue</t>
-  </si>
-  <si>
-    <t>LinkedTransferQueue</t>
-  </si>
-  <si>
-    <t>Phaser</t>
-  </si>
-  <si>
-    <t>PriorityBlockingQueue</t>
-  </si>
-  <si>
-    <t>RecursiveAction</t>
-  </si>
-  <si>
-    <t>RecursiveTask</t>
-  </si>
-  <si>
-    <t>ScheduledThreadPoolExecutor</t>
-  </si>
-  <si>
-    <t>Semaphore</t>
-  </si>
-  <si>
-    <t>SynchronousQueue</t>
-  </si>
-  <si>
-    <t>ThreadLocalRandom</t>
-  </si>
-  <si>
-    <t>ThreadPoolExecutor</t>
-  </si>
-  <si>
-    <t>ThreadPoolExecutor.AbortPolicy</t>
-  </si>
-  <si>
-    <t>ThreadPoolExecutor.CallerRunsPolicy</t>
-  </si>
-  <si>
-    <t>ThreadPoolExecutor.DiscardOldestPolicy</t>
-  </si>
-  <si>
-    <t>ThreadPoolExecutor.DiscardPolicy</t>
+    <t>SecureDirectoryStream</t>
+  </si>
+  <si>
+    <t>FileAttributeView</t>
+  </si>
+  <si>
+    <t>MappedByteBuffer</t>
+  </si>
+  <si>
+    <t>NetworkChannel</t>
+  </si>
+  <si>
+    <t>Watchable</t>
+  </si>
+  <si>
+    <t>FileOwnerAttributeView</t>
+  </si>
+  <si>
+    <t>ShortBuffer</t>
+  </si>
+  <si>
+    <t>ReadableByteChannel</t>
+  </si>
+  <si>
+    <t>CharacterCodingException</t>
+  </si>
+  <si>
+    <t>WatchEvent</t>
+  </si>
+  <si>
+    <t>FileStoreAttributeView</t>
+  </si>
+  <si>
+    <t>ScatteringByteChannel</t>
+  </si>
+  <si>
+    <t>IllegalCharsetNameException</t>
+  </si>
+  <si>
+    <t>WatchEvent.Kind</t>
+  </si>
+  <si>
+    <t>GroupPrincipal</t>
+  </si>
+  <si>
+    <t>SeekableByteChannel</t>
+  </si>
+  <si>
+    <t>MalformedInputException</t>
+  </si>
+  <si>
+    <t>WatchEvent.Modifier</t>
+  </si>
+  <si>
+    <t>PosixFileAttributes</t>
+  </si>
+  <si>
+    <t>WritableByteChannel</t>
+  </si>
+  <si>
+    <t>UnmappableCharacterException</t>
+  </si>
+  <si>
+    <t>WatchKey</t>
+  </si>
+  <si>
+    <t>PosixFileAttributeView</t>
+  </si>
+  <si>
+    <t>BufferOverflowException</t>
+  </si>
+  <si>
+    <t>UnsupportedCharsetException</t>
+  </si>
+  <si>
+    <t>WatchService</t>
+  </si>
+  <si>
+    <t>UserDefinedFileAttributeView</t>
+  </si>
+  <si>
+    <t>BufferUnderflowException</t>
+  </si>
+  <si>
+    <t>UserPrincipal</t>
+  </si>
+  <si>
+    <t>InvalidMarkException</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Errors</t>
+    </r>
+  </si>
+  <si>
+    <t>ReadOnlyBufferException</t>
+  </si>
+  <si>
+    <t>AsynchronousChannelGroup</t>
+  </si>
+  <si>
+    <t>AsynchronousFileChannel</t>
+  </si>
+  <si>
+    <t>CoderMalfunctionError</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>AsynchronousServerSocketChannel</t>
+  </si>
+  <si>
+    <t>FileStore</t>
+  </si>
+  <si>
+    <t>AclEntry</t>
+  </si>
+  <si>
+    <t>AsynchronousSocketChannel</t>
+  </si>
+  <si>
+    <t>FileSystem</t>
+  </si>
+  <si>
+    <t>AclEntry.Builder</t>
+  </si>
+  <si>
+    <t>Channels</t>
+  </si>
+  <si>
+    <t>FileSystems</t>
+  </si>
+  <si>
+    <t>FileTime</t>
+  </si>
+  <si>
+    <t>DatagramChannel</t>
+  </si>
+  <si>
+    <t>LinkPermission</t>
+  </si>
+  <si>
+    <t>PosixFilePermissions</t>
+  </si>
+  <si>
+    <t>FileChannel</t>
+  </si>
+  <si>
+    <t>Paths</t>
+  </si>
+  <si>
+    <t>UserPrincipalLookupService</t>
+  </si>
+  <si>
+    <t>FileChannel.MapMode</t>
+  </si>
+  <si>
+    <t>SimpleFileVisitor</t>
+  </si>
+  <si>
+    <t>FileLock</t>
+  </si>
+  <si>
+    <t>StandardWatchEventKinds</t>
   </si>
   <si>
     <r>
@@ -323,19 +369,469 @@
     </r>
   </si>
   <si>
+    <t>MembershipKey</t>
+  </si>
+  <si>
+    <t>Pipe</t>
+  </si>
+  <si>
+    <t>AclEntryFlag</t>
+  </si>
+  <si>
+    <t>Pipe.SinkChannel</t>
+  </si>
+  <si>
+    <t>AclEntryPermission</t>
+  </si>
+  <si>
+    <t>Pipe.SourceChannel</t>
+  </si>
+  <si>
+    <t>AccessMode</t>
+  </si>
+  <si>
+    <t>AclEntryType</t>
+  </si>
+  <si>
+    <t>SelectableChannel</t>
+  </si>
+  <si>
+    <t>FileVisitOption</t>
+  </si>
+  <si>
+    <t>PosixFilePermission</t>
+  </si>
+  <si>
+    <t>SelectionKey</t>
+  </si>
+  <si>
+    <t>FileVisitResult</t>
+  </si>
+  <si>
+    <t>Selector</t>
+  </si>
+  <si>
+    <t>LinkOption</t>
+  </si>
+  <si>
+    <t>ServerSocketChannel</t>
+  </si>
+  <si>
+    <t>StandardCopyOption</t>
+  </si>
+  <si>
+    <t>SocketChannel</t>
+  </si>
+  <si>
+    <t>StandardOpenOption</t>
+  </si>
+  <si>
+    <t>UserPrincipalNotFoundException</t>
+  </si>
+  <si>
+    <t>AcceptPendingException</t>
+  </si>
+  <si>
+    <t>AccessDeniedException</t>
+  </si>
+  <si>
+    <t>AlreadyBoundException</t>
+  </si>
+  <si>
+    <t>AtomicMoveNotSupportedException</t>
+  </si>
+  <si>
+    <t>AlreadyConnectedException</t>
+  </si>
+  <si>
+    <t>ClosedDirectoryStreamException</t>
+  </si>
+  <si>
+    <t>AsynchronousCloseException</t>
+  </si>
+  <si>
+    <t>ClosedFileSystemException</t>
+  </si>
+  <si>
+    <t>CancelledKeyException</t>
+  </si>
+  <si>
+    <t>ClosedWatchServiceException</t>
+  </si>
+  <si>
+    <t>ClosedByInterruptException</t>
+  </si>
+  <si>
+    <t>DirectoryIteratorException</t>
+  </si>
+  <si>
+    <t>ClosedChannelException</t>
+  </si>
+  <si>
+    <t>DirectoryNotEmptyException</t>
+  </si>
+  <si>
+    <t>ClosedSelectorException</t>
+  </si>
+  <si>
+    <t>FileAlreadyExistsException</t>
+  </si>
+  <si>
+    <t>ConnectionPendingException</t>
+  </si>
+  <si>
+    <t>FileSystemAlreadyExistsException</t>
+  </si>
+  <si>
+    <t>FileLockInterruptionException</t>
+  </si>
+  <si>
+    <t>FileSystemException</t>
+  </si>
+  <si>
+    <t>IllegalBlockingModeException</t>
+  </si>
+  <si>
+    <t>FileSystemLoopException</t>
+  </si>
+  <si>
+    <t>IllegalChannelGroupException</t>
+  </si>
+  <si>
+    <t>FileSystemNotFoundException</t>
+  </si>
+  <si>
+    <t>IllegalSelectorException</t>
+  </si>
+  <si>
+    <t>InvalidPathException</t>
+  </si>
+  <si>
+    <t>InterruptedByTimeoutException</t>
+  </si>
+  <si>
+    <t>NoSuchFileException</t>
+  </si>
+  <si>
+    <t>NoConnectionPendingException</t>
+  </si>
+  <si>
+    <t>NotDirectoryException</t>
+  </si>
+  <si>
+    <t>NonReadableChannelException</t>
+  </si>
+  <si>
+    <t>NotLinkException</t>
+  </si>
+  <si>
+    <t>NonWritableChannelException</t>
+  </si>
+  <si>
+    <t>ProviderMismatchException</t>
+  </si>
+  <si>
+    <t>NotYetBoundException</t>
+  </si>
+  <si>
+    <t>ProviderNotFoundException</t>
+  </si>
+  <si>
+    <t>NotYetConnectedException</t>
+  </si>
+  <si>
+    <t>ReadOnlyFileSystemException</t>
+  </si>
+  <si>
+    <t>OverlappingFileLockException</t>
+  </si>
+  <si>
+    <t>ReadPendingException</t>
+  </si>
+  <si>
+    <t>ShutdownChannelGroupException</t>
+  </si>
+  <si>
+    <t>UnresolvedAddressException</t>
+  </si>
+  <si>
+    <t>UnsupportedAddressTypeException</t>
+  </si>
+  <si>
+    <t>WritePendingException</t>
+  </si>
+  <si>
+    <t>java.util.concurrent</t>
+  </si>
+  <si>
+    <t>java.util.concurrent.atomic</t>
+  </si>
+  <si>
+    <t>java.util.concurrent.locks</t>
+  </si>
+  <si>
+    <t>BlockingDeque</t>
+  </si>
+  <si>
+    <t>AtomicBoolean</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>BlockingQueue</t>
+  </si>
+  <si>
+    <t>AtomicInteger</t>
+  </si>
+  <si>
+    <t>Lock</t>
+  </si>
+  <si>
+    <t>Callable</t>
+  </si>
+  <si>
+    <t>AtomicIntegerArray</t>
+  </si>
+  <si>
+    <t>ReadWriteLock</t>
+  </si>
+  <si>
+    <t>CompletableFuture.AsynchronousCompletionTask</t>
+  </si>
+  <si>
+    <t>AtomicIntegerFieldUpdater</t>
+  </si>
+  <si>
+    <t>CompletionService</t>
+  </si>
+  <si>
+    <t>AtomicLong</t>
+  </si>
+  <si>
+    <t>CompletionStage</t>
+  </si>
+  <si>
+    <t>AtomicLongArray</t>
+  </si>
+  <si>
+    <t>ConcurrentMap</t>
+  </si>
+  <si>
+    <t>AtomicLongFieldUpdater</t>
+  </si>
+  <si>
+    <t>AbstractOwnableSynchronizer</t>
+  </si>
+  <si>
+    <t>ConcurrentNavigableMap</t>
+  </si>
+  <si>
+    <t>AtomicMarkableReference</t>
+  </si>
+  <si>
+    <t>AbstractQueuedLongSynchronizer</t>
+  </si>
+  <si>
+    <t>Delayed</t>
+  </si>
+  <si>
+    <t>AtomicReference</t>
+  </si>
+  <si>
+    <t>AbstractQueuedSynchronizer</t>
+  </si>
+  <si>
+    <t>Executor</t>
+  </si>
+  <si>
+    <t>AtomicReferenceArray</t>
+  </si>
+  <si>
+    <t>LockSupport</t>
+  </si>
+  <si>
+    <t>ExecutorService</t>
+  </si>
+  <si>
+    <t>AtomicReferenceFieldUpdater</t>
+  </si>
+  <si>
+    <t>ReentrantLock</t>
+  </si>
+  <si>
+    <t>ForkJoinPool.ForkJoinWorkerThreadFactory</t>
+  </si>
+  <si>
+    <t>AtomicStampedReference</t>
+  </si>
+  <si>
+    <t>ReentrantReadWriteLock</t>
+  </si>
+  <si>
+    <t>ForkJoinPool.ManagedBlocker</t>
+  </si>
+  <si>
+    <t>DoubleAccumulator</t>
+  </si>
+  <si>
+    <t>ReentrantReadWriteLock.ReadLock</t>
+  </si>
+  <si>
+    <t>Future</t>
+  </si>
+  <si>
+    <t>DoubleAdder</t>
+  </si>
+  <si>
+    <t>ReentrantReadWriteLock.WriteLock</t>
+  </si>
+  <si>
+    <t>RejectedExecutionHandler</t>
+  </si>
+  <si>
+    <t>LongAccumulator</t>
+  </si>
+  <si>
+    <t>StampedLock</t>
+  </si>
+  <si>
+    <t>RunnableFuture</t>
+  </si>
+  <si>
+    <t>LongAdder</t>
+  </si>
+  <si>
+    <t>RunnableScheduledFuture</t>
+  </si>
+  <si>
+    <t>ScheduledExecutorService</t>
+  </si>
+  <si>
+    <t>ScheduledFuture</t>
+  </si>
+  <si>
+    <t>ThreadFactory</t>
+  </si>
+  <si>
+    <t>TransferQueue</t>
+  </si>
+  <si>
+    <t>AbstractExecutorService</t>
+  </si>
+  <si>
+    <t>ArrayBlockingQueue</t>
+  </si>
+  <si>
+    <t>CompletableFuture</t>
+  </si>
+  <si>
+    <t>ConcurrentHashMap</t>
+  </si>
+  <si>
+    <t>ConcurrentHashMap.KeySetView</t>
+  </si>
+  <si>
+    <t>ConcurrentLinkedDeque</t>
+  </si>
+  <si>
+    <t>ConcurrentLinkedQueue</t>
+  </si>
+  <si>
+    <t>ConcurrentSkipListMap</t>
+  </si>
+  <si>
+    <t>ConcurrentSkipListSet</t>
+  </si>
+  <si>
+    <t>CopyOnWriteArrayList</t>
+  </si>
+  <si>
+    <t>CopyOnWriteArraySet</t>
+  </si>
+  <si>
+    <t>CountDownLatch</t>
+  </si>
+  <si>
+    <t>CountedCompleter</t>
+  </si>
+  <si>
+    <t>CyclicBarrier</t>
+  </si>
+  <si>
+    <t>DelayQueue</t>
+  </si>
+  <si>
+    <t>Exchanger</t>
+  </si>
+  <si>
+    <t>ExecutorCompletionService</t>
+  </si>
+  <si>
+    <t>Executors</t>
+  </si>
+  <si>
+    <t>ForkJoinPool</t>
+  </si>
+  <si>
+    <t>ForkJoinTask</t>
+  </si>
+  <si>
+    <t>ForkJoinWorkerThread</t>
+  </si>
+  <si>
+    <t>FutureTask</t>
+  </si>
+  <si>
+    <t>LinkedBlockingDeque</t>
+  </si>
+  <si>
+    <t>LinkedBlockingQueue</t>
+  </si>
+  <si>
+    <t>LinkedTransferQueue</t>
+  </si>
+  <si>
+    <t>Phaser</t>
+  </si>
+  <si>
+    <t>PriorityBlockingQueue</t>
+  </si>
+  <si>
+    <t>RecursiveAction</t>
+  </si>
+  <si>
+    <t>RecursiveTask</t>
+  </si>
+  <si>
+    <t>ScheduledThreadPoolExecutor</t>
+  </si>
+  <si>
+    <t>Semaphore</t>
+  </si>
+  <si>
+    <t>SynchronousQueue</t>
+  </si>
+  <si>
+    <t>ThreadLocalRandom</t>
+  </si>
+  <si>
+    <t>ThreadPoolExecutor</t>
+  </si>
+  <si>
+    <t>ThreadPoolExecutor.AbortPolicy</t>
+  </si>
+  <si>
+    <t>ThreadPoolExecutor.CallerRunsPolicy</t>
+  </si>
+  <si>
+    <t>ThreadPoolExecutor.DiscardOldestPolicy</t>
+  </si>
+  <si>
+    <t>ThreadPoolExecutor.DiscardPolicy</t>
+  </si>
+  <si>
     <t>TimeUnit</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9.75"/>
-        <color rgb="FF353833"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Exceptions</t>
-    </r>
   </si>
   <si>
     <t>BrokenBarrierException</t>
@@ -1362,6 +1858,675 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:P65"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="4:4">
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="25.2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="7:7">
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" t="s">
+        <v>15</v>
+      </c>
+      <c r="P5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" ht="25.2" spans="1:16">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" t="s">
+        <v>50</v>
+      </c>
+      <c r="P12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" t="s">
+        <v>55</v>
+      </c>
+      <c r="P13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="4:16">
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="J14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" t="s">
+        <v>59</v>
+      </c>
+      <c r="P14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" ht="25.2" spans="1:16">
+      <c r="A15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" t="s">
+        <v>63</v>
+      </c>
+      <c r="P15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="4:16">
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="J16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" t="s">
+        <v>67</v>
+      </c>
+      <c r="P16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17" t="s">
+        <v>71</v>
+      </c>
+      <c r="P17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="4:13">
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" t="s">
+        <v>80</v>
+      </c>
+      <c r="M21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16">
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="M22" t="s">
+        <v>83</v>
+      </c>
+      <c r="P22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16">
+      <c r="D23" t="s">
+        <v>85</v>
+      </c>
+      <c r="M23" t="s">
+        <v>86</v>
+      </c>
+      <c r="P23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16">
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="M24" t="s">
+        <v>89</v>
+      </c>
+      <c r="P24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="4:16">
+      <c r="D25" t="s">
+        <v>91</v>
+      </c>
+      <c r="M25" t="s">
+        <v>92</v>
+      </c>
+      <c r="P25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="4:16">
+      <c r="D26" t="s">
+        <v>94</v>
+      </c>
+      <c r="M26" t="s">
+        <v>95</v>
+      </c>
+      <c r="P26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13">
+      <c r="D27" t="s">
+        <v>97</v>
+      </c>
+      <c r="M27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="4:16">
+      <c r="D28" t="s">
+        <v>99</v>
+      </c>
+      <c r="M28" t="s">
+        <v>100</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="4:4">
+      <c r="D29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="4:16">
+      <c r="D30" t="s">
+        <v>103</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="4:16">
+      <c r="D31" t="s">
+        <v>105</v>
+      </c>
+      <c r="P31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="4:16">
+      <c r="D32" t="s">
+        <v>107</v>
+      </c>
+      <c r="M32" t="s">
+        <v>108</v>
+      </c>
+      <c r="P32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="4:16">
+      <c r="D33" t="s">
+        <v>110</v>
+      </c>
+      <c r="M33" t="s">
+        <v>111</v>
+      </c>
+      <c r="P33" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="4:13">
+      <c r="D34" t="s">
+        <v>113</v>
+      </c>
+      <c r="M34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" ht="25.2" spans="4:16">
+      <c r="D35" t="s">
+        <v>115</v>
+      </c>
+      <c r="M35" t="s">
+        <v>116</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="4:13">
+      <c r="D36" t="s">
+        <v>117</v>
+      </c>
+      <c r="M36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="4:16">
+      <c r="D37" t="s">
+        <v>119</v>
+      </c>
+      <c r="M37" t="s">
+        <v>120</v>
+      </c>
+      <c r="P37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" ht="25.2" spans="4:13">
+      <c r="D39" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="4:13">
+      <c r="D41" t="s">
+        <v>122</v>
+      </c>
+      <c r="M41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="4:13">
+      <c r="D42" t="s">
+        <v>124</v>
+      </c>
+      <c r="M42" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="4:13">
+      <c r="D43" t="s">
+        <v>126</v>
+      </c>
+      <c r="M43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="4:13">
+      <c r="D44" t="s">
+        <v>128</v>
+      </c>
+      <c r="M44" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="4:13">
+      <c r="D45" t="s">
+        <v>130</v>
+      </c>
+      <c r="M45" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="4:13">
+      <c r="D46" t="s">
+        <v>132</v>
+      </c>
+      <c r="M46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="4:13">
+      <c r="D47" t="s">
+        <v>134</v>
+      </c>
+      <c r="M47" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="4:13">
+      <c r="D48" t="s">
+        <v>136</v>
+      </c>
+      <c r="M48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="4:13">
+      <c r="D49" t="s">
+        <v>138</v>
+      </c>
+      <c r="M49" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="50" spans="4:13">
+      <c r="D50" t="s">
+        <v>140</v>
+      </c>
+      <c r="M50" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="4:13">
+      <c r="D51" t="s">
+        <v>142</v>
+      </c>
+      <c r="M51" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="4:13">
+      <c r="D52" t="s">
+        <v>144</v>
+      </c>
+      <c r="M52" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" spans="4:13">
+      <c r="D53" t="s">
+        <v>146</v>
+      </c>
+      <c r="M53" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="4:13">
+      <c r="D54" t="s">
+        <v>148</v>
+      </c>
+      <c r="M54" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="4:13">
+      <c r="D55" t="s">
+        <v>150</v>
+      </c>
+      <c r="M55" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="4:13">
+      <c r="D56" t="s">
+        <v>152</v>
+      </c>
+      <c r="M56" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="57" spans="4:13">
+      <c r="D57" t="s">
+        <v>154</v>
+      </c>
+      <c r="M57" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="58" spans="4:13">
+      <c r="D58" t="s">
+        <v>156</v>
+      </c>
+      <c r="M58" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="59" spans="4:13">
+      <c r="D59" t="s">
+        <v>158</v>
+      </c>
+      <c r="M59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="4:4">
+      <c r="D60" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="4:4">
+      <c r="D61" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4">
+      <c r="D62" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="64" spans="4:4">
+      <c r="D64" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="65" spans="4:4">
+      <c r="D65" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
@@ -1372,456 +2537,456 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="D1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G2" s="1" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="G4" t="s">
-        <v>7</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>4</v>
+        <v>181</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>188</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>193</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>194</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>196</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>197</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>199</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="G15" t="s">
-        <v>37</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>202</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>203</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>205</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>211</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="2" t="s">
-        <v>4</v>
+      <c r="A26" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>78</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>79</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>80</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>246</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>247</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>84</v>
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>85</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>88</v>
+        <v>252</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>90</v>
+        <v>254</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>91</v>
+        <v>255</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="2" t="s">
-        <v>92</v>
+      <c r="A67" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>256</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="2" t="s">
-        <v>94</v>
+      <c r="A71" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>95</v>
+        <v>257</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>96</v>
+        <v>258</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>97</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>98</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>99</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>100</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -1830,7 +2995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A27"/>
@@ -1838,112 +3003,112 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" ht="25.2" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/java/jdk8/javase_api_doc.xlsx
+++ b/java/jdk8/javase_api_doc.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564"/>
+    <workbookView windowWidth="22368" windowHeight="9564" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="303">
   <si>
     <t>java.nio.channels</t>
   </si>
@@ -559,6 +560,78 @@
   </si>
   <si>
     <t>WritePendingException</t>
+  </si>
+  <si>
+    <t>javax.annotation</t>
+  </si>
+  <si>
+    <t>javax.annotation.processing</t>
+  </si>
+  <si>
+    <t>Resource.AuthenticationType</t>
+  </si>
+  <si>
+    <t>Completion</t>
+  </si>
+  <si>
+    <t>Filer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Annotation Types</t>
+    </r>
+  </si>
+  <si>
+    <t>Messager</t>
+  </si>
+  <si>
+    <t>ProcessingEnvironment</t>
+  </si>
+  <si>
+    <t>Generated</t>
+  </si>
+  <si>
+    <t>Processor</t>
+  </si>
+  <si>
+    <t>PostConstruct</t>
+  </si>
+  <si>
+    <t>RoundEnvironment</t>
+  </si>
+  <si>
+    <t>PreDestroy</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>Resources</t>
+  </si>
+  <si>
+    <t>AbstractProcessor</t>
+  </si>
+  <si>
+    <t>Completions</t>
+  </si>
+  <si>
+    <t>FilerException</t>
+  </si>
+  <si>
+    <t>SupportedAnnotationTypes</t>
+  </si>
+  <si>
+    <t>SupportedOptions</t>
+  </si>
+  <si>
+    <t>SupportedSourceVersion</t>
   </si>
   <si>
     <t>java.util.concurrent</t>
@@ -1273,12 +1346,40 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1390,7 +1491,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1420,7 +1521,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1438,28 +1539,28 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1468,10 +1569,10 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1529,14 +1630,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1867,22 +1974,22 @@
       </c>
     </row>
     <row r="2" ht="25.2" spans="1:16">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2026,7 +2133,7 @@
       <c r="D11" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="1" t="s">
         <v>45</v>
       </c>
       <c r="M11" t="s">
@@ -2082,7 +2189,7 @@
       </c>
     </row>
     <row r="15" ht="25.2" spans="1:16">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D15" t="s">
@@ -2130,7 +2237,7 @@
       <c r="A18" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P18" t="s">
@@ -2141,10 +2248,10 @@
       <c r="A19" t="s">
         <v>75</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2155,7 +2262,7 @@
       <c r="D20" t="s">
         <v>78</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="P20" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2240,7 +2347,7 @@
       <c r="M28" t="s">
         <v>100</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="P28" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2253,7 +2360,7 @@
       <c r="D30" t="s">
         <v>103</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="M30" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P30" t="s">
@@ -2305,7 +2412,7 @@
       <c r="M35" t="s">
         <v>116</v>
       </c>
-      <c r="P35" s="2" t="s">
+      <c r="P35" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2329,10 +2436,10 @@
       </c>
     </row>
     <row r="39" ht="25.2" spans="4:13">
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="M39" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2525,6 +2632,226 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" ht="25.2" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" ht="25.2" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="4:6">
+      <c r="D13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="4:6">
+      <c r="D14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="4:6">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" ht="25.2" spans="4:6">
+      <c r="D16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="4:6">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="4:6">
+      <c r="D18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="4:6">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" ht="25.2" spans="4:6">
+      <c r="D20" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="4:6">
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="4:6">
+      <c r="D22" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="4:6">
+      <c r="D23" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="4:6">
+      <c r="D24" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G78"/>
@@ -2537,13 +2864,13 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="D1" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="G1" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2559,51 +2886,51 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G4" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="G6" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="D8" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>1</v>
@@ -2611,142 +2938,142 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="G10" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="D11" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="G11" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="D12" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="G12" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="D13" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="G13" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="D14" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="G14" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="D15" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="G15" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="D16" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="G16" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="D17" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="G17" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="D18" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="G18" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="D19" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -2756,192 +3083,192 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -2951,7 +3278,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -2961,32 +3288,32 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -2995,7 +3322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A27"/>
@@ -3003,7 +3330,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3013,77 +3340,77 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -3093,12 +3420,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" ht="25.2" spans="1:1">
@@ -3108,7 +3435,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/java/jdk8/javase_api_doc.xlsx
+++ b/java/jdk8/javase_api_doc.xlsx
@@ -1,25 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="10455" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="nio_channels" sheetId="3" r:id="rId1"/>
+    <sheet name="javax_annotation" sheetId="4" r:id="rId2"/>
+    <sheet name="util_concurrent" sheetId="1" r:id="rId3"/>
+    <sheet name="time" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="314">
+  <si>
+    <t>java.nio</t>
+  </si>
   <si>
     <t>java.nio.channels</t>
+  </si>
+  <si>
+    <t>java.nio.channels.spi</t>
+  </si>
+  <si>
+    <t>java.nio.charset</t>
+  </si>
+  <si>
+    <t>java.nio.charset.spi</t>
+  </si>
+  <si>
+    <t>java.nio.file</t>
+  </si>
+  <si>
+    <t>java.nio.file.attribute</t>
+  </si>
+  <si>
+    <t>java.nio.file.spi</t>
   </si>
   <si>
     <r>
@@ -46,103 +80,112 @@
     </r>
   </si>
   <si>
+    <t>Buffer</t>
+  </si>
+  <si>
+    <t>AsynchronousByteChannel  AsynchronousChannel子接口</t>
+  </si>
+  <si>
     <t>AbstractInterruptibleChannel</t>
   </si>
   <si>
+    <t>Charset</t>
+  </si>
+  <si>
+    <t>CharsetProvider</t>
+  </si>
+  <si>
+    <t>CopyOption</t>
+  </si>
+  <si>
+    <t>AclFileAttributeView</t>
+  </si>
+  <si>
+    <t>FileSystemProvider</t>
+  </si>
+  <si>
+    <t>ByteBuffer</t>
+  </si>
+  <si>
+    <t>AsynchronousChannel</t>
+  </si>
+  <si>
     <t>AbstractSelectableChannel</t>
   </si>
   <si>
-    <t>Buffer</t>
-  </si>
-  <si>
-    <t>AsynchronousByteChannel</t>
+    <t>CharsetDecoder</t>
+  </si>
+  <si>
+    <t>DirectoryStream</t>
+  </si>
+  <si>
+    <t>AttributeView</t>
+  </si>
+  <si>
+    <t>FileTypeDetector</t>
+  </si>
+  <si>
+    <t>ByteOrder</t>
+  </si>
+  <si>
+    <t>ByteChannel</t>
   </si>
   <si>
     <t>AbstractSelectionKey</t>
   </si>
   <si>
-    <t>Charset</t>
-  </si>
-  <si>
-    <t>CopyOption</t>
-  </si>
-  <si>
-    <t>AclFileAttributeView</t>
-  </si>
-  <si>
-    <t>ByteBuffer</t>
-  </si>
-  <si>
-    <t>AsynchronousChannel</t>
+    <t>CharsetEncoder</t>
+  </si>
+  <si>
+    <t>DirectoryStream.Filter</t>
+  </si>
+  <si>
+    <t>BasicFileAttributes</t>
+  </si>
+  <si>
+    <t>CharBuffer</t>
+  </si>
+  <si>
+    <t>Channel</t>
   </si>
   <si>
     <t>AbstractSelector</t>
   </si>
   <si>
-    <t>CharsetDecoder</t>
-  </si>
-  <si>
-    <t>DirectoryStream</t>
-  </si>
-  <si>
-    <t>AttributeView</t>
-  </si>
-  <si>
-    <t>ByteOrder</t>
-  </si>
-  <si>
-    <t>ByteChannel</t>
+    <t>CoderResult</t>
+  </si>
+  <si>
+    <t>FileVisitor</t>
+  </si>
+  <si>
+    <t>BasicFileAttributeView</t>
+  </si>
+  <si>
+    <t>DoubleBuffer</t>
+  </si>
+  <si>
+    <t>CompletionHandler</t>
   </si>
   <si>
     <t>AsynchronousChannelProvider</t>
   </si>
   <si>
-    <t>CharsetEncoder</t>
-  </si>
-  <si>
-    <t>DirectoryStream.Filter</t>
-  </si>
-  <si>
-    <t>BasicFileAttributes</t>
-  </si>
-  <si>
-    <t>CharBuffer</t>
-  </si>
-  <si>
-    <t>Channel</t>
+    <t>CodingErrorAction</t>
+  </si>
+  <si>
+    <t>OpenOption</t>
+  </si>
+  <si>
+    <t>DosFileAttributes</t>
+  </si>
+  <si>
+    <t>FloatBuffer</t>
+  </si>
+  <si>
+    <t>GatheringByteChannel</t>
   </si>
   <si>
     <t>SelectorProvider</t>
-  </si>
-  <si>
-    <t>CoderResult</t>
-  </si>
-  <si>
-    <t>FileVisitor</t>
-  </si>
-  <si>
-    <t>BasicFileAttributeView</t>
-  </si>
-  <si>
-    <t>DoubleBuffer</t>
-  </si>
-  <si>
-    <t>CompletionHandler</t>
-  </si>
-  <si>
-    <t>CodingErrorAction</t>
-  </si>
-  <si>
-    <t>OpenOption</t>
-  </si>
-  <si>
-    <t>DosFileAttributes</t>
-  </si>
-  <si>
-    <t>FloatBuffer</t>
-  </si>
-  <si>
-    <t>GatheringByteChannel</t>
   </si>
   <si>
     <t>StandardCharsets</t>
@@ -193,6 +236,9 @@
     <t>MappedByteBuffer</t>
   </si>
   <si>
+    <t>mmap</t>
+  </si>
+  <si>
     <t>NetworkChannel</t>
   </si>
   <si>
@@ -985,7 +1031,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1008,34 +1054,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -1049,14 +1067,6 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1096,6 +1106,21 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1146,13 +1171,34 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1161,31 +1207,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1197,19 +1219,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1227,31 +1237,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1275,6 +1273,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1287,7 +1297,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1311,7 +1345,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1330,6 +1376,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1384,21 +1436,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -1427,6 +1464,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1485,158 +1537,161 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1644,57 +1699,60 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1965,664 +2023,718 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P65"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:O65"/>
+  <sheetFormatPr defaultColWidth="8.88495575221239" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="22.5044247787611" customWidth="1"/>
+    <col min="3" max="3" width="35.0530973451327" customWidth="1"/>
+    <col min="5" max="5" width="30.3362831858407" customWidth="1"/>
+    <col min="7" max="7" width="27.0265486725664" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="30.4778761061947" customWidth="1"/>
+    <col min="11" max="11" width="35.716814159292" customWidth="1"/>
+    <col min="13" max="13" width="29.2743362831858" customWidth="1"/>
+    <col min="15" max="15" width="18.9911504424779" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="4:4">
-      <c r="D1" t="s">
+    <row r="1" s="2" customFormat="1" spans="1:15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="25.2" spans="1:16">
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="7:7">
-      <c r="G3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>9</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:15">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" ht="24.75" spans="1:13">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="K11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="3:13">
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" ht="24.75" spans="1:13">
+      <c r="A15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13">
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" t="s">
+        <v>82</v>
+      </c>
+      <c r="M17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M4" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" t="s">
-        <v>15</v>
-      </c>
-      <c r="P5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" t="s">
-        <v>36</v>
-      </c>
-      <c r="M9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" t="s">
-        <v>41</v>
-      </c>
-      <c r="P10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" ht="25.2" spans="1:16">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="M11" t="s">
-        <v>46</v>
-      </c>
-      <c r="P11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12" t="s">
-        <v>50</v>
-      </c>
-      <c r="P12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="M18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11">
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13">
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="K22" t="s">
+        <v>94</v>
+      </c>
+      <c r="M22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13">
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="K23" t="s">
+        <v>97</v>
+      </c>
+      <c r="M23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13">
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="K24" t="s">
+        <v>100</v>
+      </c>
+      <c r="M24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13">
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+      <c r="K25" t="s">
+        <v>103</v>
+      </c>
+      <c r="M25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13">
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+      <c r="K26" t="s">
+        <v>106</v>
+      </c>
+      <c r="M26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11">
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="K27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13">
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="K28" t="s">
+        <v>111</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13">
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M30" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13">
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
+      <c r="M31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13">
+      <c r="C32" t="s">
+        <v>118</v>
+      </c>
+      <c r="K32" t="s">
+        <v>119</v>
+      </c>
+      <c r="M32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="3:13">
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="K33" t="s">
+        <v>122</v>
+      </c>
+      <c r="M33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="3:11">
+      <c r="C34" t="s">
+        <v>124</v>
+      </c>
+      <c r="K34" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" ht="24.75" spans="3:13">
+      <c r="C35" t="s">
+        <v>126</v>
+      </c>
+      <c r="K35" t="s">
+        <v>127</v>
+      </c>
+      <c r="M35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="4:16">
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
-      <c r="J14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" t="s">
-        <v>59</v>
-      </c>
-      <c r="P14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" ht="25.2" spans="1:16">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="J15" t="s">
-        <v>62</v>
-      </c>
-      <c r="M15" t="s">
-        <v>63</v>
-      </c>
-      <c r="P15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="4:16">
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
-      <c r="J16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M16" t="s">
-        <v>67</v>
-      </c>
-      <c r="P16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" t="s">
-        <v>69</v>
-      </c>
-      <c r="J17" t="s">
-        <v>70</v>
-      </c>
-      <c r="M17" t="s">
-        <v>71</v>
-      </c>
-      <c r="P17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" t="s">
-        <v>78</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="4:13">
-      <c r="D21" t="s">
-        <v>79</v>
-      </c>
-      <c r="J21" t="s">
-        <v>80</v>
-      </c>
-      <c r="M21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="4:16">
-      <c r="D22" t="s">
-        <v>82</v>
-      </c>
-      <c r="M22" t="s">
-        <v>83</v>
-      </c>
-      <c r="P22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="4:16">
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-      <c r="M23" t="s">
-        <v>86</v>
-      </c>
-      <c r="P23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="4:16">
-      <c r="D24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M24" t="s">
-        <v>89</v>
-      </c>
-      <c r="P24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="4:16">
-      <c r="D25" t="s">
-        <v>91</v>
-      </c>
-      <c r="M25" t="s">
-        <v>92</v>
-      </c>
-      <c r="P25" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="4:16">
-      <c r="D26" t="s">
-        <v>94</v>
-      </c>
-      <c r="M26" t="s">
-        <v>95</v>
-      </c>
-      <c r="P26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="4:13">
-      <c r="D27" t="s">
-        <v>97</v>
-      </c>
-      <c r="M27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="4:16">
-      <c r="D28" t="s">
-        <v>99</v>
-      </c>
-      <c r="M28" t="s">
-        <v>100</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="4:4">
-      <c r="D29" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="4:16">
-      <c r="D30" t="s">
-        <v>103</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="4:16">
-      <c r="D31" t="s">
-        <v>105</v>
-      </c>
-      <c r="P31" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="32" spans="4:16">
-      <c r="D32" t="s">
-        <v>107</v>
-      </c>
-      <c r="M32" t="s">
-        <v>108</v>
-      </c>
-      <c r="P32" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="4:16">
-      <c r="D33" t="s">
-        <v>110</v>
-      </c>
-      <c r="M33" t="s">
-        <v>111</v>
-      </c>
-      <c r="P33" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="4:13">
-      <c r="D34" t="s">
-        <v>113</v>
-      </c>
-      <c r="M34" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" ht="25.2" spans="4:16">
-      <c r="D35" t="s">
-        <v>115</v>
-      </c>
-      <c r="M35" t="s">
-        <v>116</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="4:13">
-      <c r="D36" t="s">
-        <v>117</v>
-      </c>
-      <c r="M36" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="4:16">
-      <c r="D37" t="s">
-        <v>119</v>
+    </row>
+    <row r="36" spans="3:11">
+      <c r="C36" t="s">
+        <v>128</v>
+      </c>
+      <c r="K36" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="3:13">
+      <c r="C37" t="s">
+        <v>130</v>
+      </c>
+      <c r="K37" t="s">
+        <v>131</v>
       </c>
       <c r="M37" t="s">
-        <v>120</v>
-      </c>
-      <c r="P37" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" ht="25.2" spans="4:13">
-      <c r="D39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="4:13">
-      <c r="D41" t="s">
-        <v>122</v>
-      </c>
-      <c r="M41" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="4:13">
-      <c r="D42" t="s">
-        <v>124</v>
-      </c>
-      <c r="M42" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="43" spans="4:13">
-      <c r="D43" t="s">
-        <v>126</v>
-      </c>
-      <c r="M43" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" spans="4:13">
-      <c r="D44" t="s">
-        <v>128</v>
-      </c>
-      <c r="M44" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="45" spans="4:13">
-      <c r="D45" t="s">
-        <v>130</v>
-      </c>
-      <c r="M45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" spans="4:13">
-      <c r="D46" t="s">
         <v>132</v>
       </c>
-      <c r="M46" t="s">
+    </row>
+    <row r="39" ht="24.75" spans="3:11">
+      <c r="C39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="3:11">
+      <c r="C41" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="47" spans="4:13">
-      <c r="D47" t="s">
+      <c r="K41" t="s">
         <v>134</v>
       </c>
-      <c r="M47" t="s">
+    </row>
+    <row r="42" spans="3:11">
+      <c r="C42" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="48" spans="4:13">
-      <c r="D48" t="s">
+      <c r="K42" t="s">
         <v>136</v>
       </c>
-      <c r="M48" t="s">
+    </row>
+    <row r="43" spans="3:11">
+      <c r="C43" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="49" spans="4:13">
-      <c r="D49" t="s">
+      <c r="K43" t="s">
         <v>138</v>
       </c>
-      <c r="M49" t="s">
+    </row>
+    <row r="44" spans="3:11">
+      <c r="C44" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="50" spans="4:13">
-      <c r="D50" t="s">
+      <c r="K44" t="s">
         <v>140</v>
       </c>
-      <c r="M50" t="s">
+    </row>
+    <row r="45" spans="3:11">
+      <c r="C45" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="51" spans="4:13">
-      <c r="D51" t="s">
+      <c r="K45" t="s">
         <v>142</v>
       </c>
-      <c r="M51" t="s">
+    </row>
+    <row r="46" spans="3:11">
+      <c r="C46" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="52" spans="4:13">
-      <c r="D52" t="s">
+      <c r="K46" t="s">
         <v>144</v>
       </c>
-      <c r="M52" t="s">
+    </row>
+    <row r="47" spans="3:11">
+      <c r="C47" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="53" spans="4:13">
-      <c r="D53" t="s">
+      <c r="K47" t="s">
         <v>146</v>
       </c>
-      <c r="M53" t="s">
+    </row>
+    <row r="48" spans="3:11">
+      <c r="C48" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="54" spans="4:13">
-      <c r="D54" t="s">
+      <c r="K48" t="s">
         <v>148</v>
       </c>
-      <c r="M54" t="s">
+    </row>
+    <row r="49" spans="3:11">
+      <c r="C49" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="55" spans="4:13">
-      <c r="D55" t="s">
+      <c r="K49" t="s">
         <v>150</v>
       </c>
-      <c r="M55" t="s">
+    </row>
+    <row r="50" spans="3:11">
+      <c r="C50" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="56" spans="4:13">
-      <c r="D56" t="s">
+      <c r="K50" t="s">
         <v>152</v>
       </c>
-      <c r="M56" t="s">
+    </row>
+    <row r="51" spans="3:11">
+      <c r="C51" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="57" spans="4:13">
-      <c r="D57" t="s">
+      <c r="K51" t="s">
         <v>154</v>
       </c>
-      <c r="M57" t="s">
+    </row>
+    <row r="52" spans="3:11">
+      <c r="C52" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="58" spans="4:13">
-      <c r="D58" t="s">
+      <c r="K52" t="s">
         <v>156</v>
       </c>
-      <c r="M58" t="s">
+    </row>
+    <row r="53" spans="3:11">
+      <c r="C53" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="59" spans="4:13">
-      <c r="D59" t="s">
+      <c r="K53" t="s">
         <v>158</v>
       </c>
-      <c r="M59" t="s">
+    </row>
+    <row r="54" spans="3:11">
+      <c r="C54" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="60" spans="4:4">
-      <c r="D60" t="s">
+      <c r="K54" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="4:4">
-      <c r="D61" t="s">
+    <row r="55" spans="3:11">
+      <c r="C55" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="62" spans="4:4">
-      <c r="D62" t="s">
+      <c r="K55" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="63" spans="4:4">
-      <c r="D63" t="s">
+    <row r="56" spans="3:11">
+      <c r="C56" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="64" spans="4:4">
-      <c r="D64" t="s">
+      <c r="K56" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="65" spans="4:4">
-      <c r="D65" t="s">
+    <row r="57" spans="3:11">
+      <c r="C57" t="s">
         <v>165</v>
+      </c>
+      <c r="K57" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" spans="3:11">
+      <c r="C58" t="s">
+        <v>167</v>
+      </c>
+      <c r="K58" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="3:11">
+      <c r="C59" t="s">
+        <v>169</v>
+      </c>
+      <c r="K59" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3">
+      <c r="C60" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3">
+      <c r="C61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3">
+      <c r="C62" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3">
+      <c r="C63" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3">
+      <c r="C64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3">
+      <c r="C65" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2635,215 +2747,219 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88495575221239" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="31.1327433628319" customWidth="1"/>
+    <col min="4" max="4" width="35.1150442477876" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" ht="25.2" spans="1:6">
-      <c r="A2" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="A4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" ht="25.2" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" ht="24.75" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="A11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="A12" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="4:6">
-      <c r="D13" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="D13" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="4:6">
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="4:6">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" ht="24.75" spans="4:6">
+      <c r="D16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="4:6">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="4:6">
+      <c r="D18" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="4:6">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" ht="24.75" spans="4:6">
+      <c r="D20" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="4:6">
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" ht="25.2" spans="4:6">
-      <c r="D16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="4:6">
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="4:6">
-      <c r="D18" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="4:6">
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" ht="25.2" spans="4:6">
-      <c r="D20" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" spans="4:6">
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="4:6">
-      <c r="D22" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="D22" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" spans="4:6">
-      <c r="D23" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="D23" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="4:6">
-      <c r="D24" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="D24" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2855,465 +2971,465 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G78"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.88495575221239" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="20.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="22.2222222222222" customWidth="1"/>
-    <col min="7" max="7" width="23.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="39.6283185840708" customWidth="1"/>
+    <col min="4" max="4" width="27.8141592920354" customWidth="1"/>
+    <col min="7" max="7" width="33.0530973451327" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G1" t="s">
-        <v>189</v>
+    <row r="1" s="2" customFormat="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="G4" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D5" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G5" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D6" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="G6" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D8" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D9" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D10" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="G10" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D11" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G11" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="G12" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G13" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D14" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="G14" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D15" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="G15" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="D16" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="G16" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D17" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="G17" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="D18" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="G18" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D19" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -3326,116 +3442,119 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A27"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.88495575221239" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="22.7787610619469" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="25" ht="25.2" spans="1:1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="25" ht="24.75" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
